--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/l_jo_uu_nl/Documents/PSR/WEBSITE/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{8C507182-54B2-BA43-8503-6188EFD09888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EC55B46-A02A-E04C-8F9D-185A34B96E99}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{8C507182-54B2-BA43-8503-6188EFD09888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F402B2CD-2000-8848-A7F5-EC0575C711EC}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19440" xr2:uid="{AC0D33F6-FE1F-474A-AAEA-EAE863AC9E26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="21">
   <si>
     <t>year</t>
   </si>
@@ -93,6 +93,12 @@
   </si>
   <si>
     <t>10.1101/2025.06.28.662111</t>
+  </si>
+  <si>
+    <t>10.1126/sciadv.aef2430</t>
+  </si>
+  <si>
+    <t>10.1016/j.chom.2026.07.009</t>
   </si>
 </sst>
 </file>
@@ -145,10 +151,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -468,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFC1B41B-A9AD-9442-9B45-C55C0DC202EF}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
@@ -670,6 +672,34 @@
         <v>5</v>
       </c>
     </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2026</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2026</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
